--- a/data/trans_camb/P19C01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 6,69</t>
+          <t>-7,52; 7,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 21,8</t>
+          <t>6,82; 22,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,9; 37,64</t>
+          <t>24,27; 38,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 12,61</t>
+          <t>-4,35; 12,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 19,64</t>
+          <t>3,46; 20,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,39; 33,07</t>
+          <t>18,1; 31,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 7,37</t>
+          <t>-3,76; 7,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 18,23</t>
+          <t>7,91; 18,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,46; 33,44</t>
+          <t>23,74; 33,43</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 19,64</t>
+          <t>-18,63; 21,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,37; 65,51</t>
+          <t>16,78; 67,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,12; 113,67</t>
+          <t>59,89; 115,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 33,78</t>
+          <t>-9,56; 35,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 53,96</t>
+          <t>7,03; 55,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,06; 91,17</t>
+          <t>38,8; 89,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 21,37</t>
+          <t>-8,75; 19,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 52,03</t>
+          <t>18,4; 53,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,69; 92,97</t>
+          <t>55,77; 94,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 13,61</t>
+          <t>-1,35; 13,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 23,33</t>
+          <t>7,06; 22,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,62; 41,73</t>
+          <t>27,84; 42,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 15,88</t>
+          <t>0,21; 15,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,03; 23,83</t>
+          <t>8,62; 23,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,71; 36,33</t>
+          <t>22,92; 37,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 12,21</t>
+          <t>0,75; 11,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 21,47</t>
+          <t>10,55; 22,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,02; 37,22</t>
+          <t>27,18; 36,59</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 52,24</t>
+          <t>-3,88; 51,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,87; 88,13</t>
+          <t>19,21; 85,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,13; 159,13</t>
+          <t>77,86; 161,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 47,45</t>
+          <t>0,46; 45,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,66; 70,55</t>
+          <t>21,67; 71,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,78; 109,47</t>
+          <t>54,49; 113,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 37,63</t>
+          <t>1,66; 36,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,98; 68,57</t>
+          <t>28,07; 70,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,95; 118,93</t>
+          <t>71,31; 116,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 5,41</t>
+          <t>-6,62; 4,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 16,59</t>
+          <t>3,75; 16,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 31,27</t>
+          <t>-14,48; 31,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 6,94</t>
+          <t>-12,43; 7,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 9,8</t>
+          <t>-11,92; 10,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 30,09</t>
+          <t>9,76; 29,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 4,11</t>
+          <t>-5,77; 4,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 13,41</t>
+          <t>2,12; 13,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 29,1</t>
+          <t>-12,97; 28,91</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 22,66</t>
+          <t>-21,89; 19,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,84; 69,49</t>
+          <t>11,56; 67,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 120,95</t>
+          <t>-49,29; 120,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 23,18</t>
+          <t>-30,07; 24,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 32,36</t>
+          <t>-30,26; 35,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,5; 105,65</t>
+          <t>23,19; 102,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 15,3</t>
+          <t>-18,26; 15,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,08; 49,23</t>
+          <t>6,29; 50,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 104,21</t>
+          <t>-42,31; 100,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 3,91</t>
+          <t>-4,12; 4,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 16,55</t>
+          <t>8,05; 16,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,98; 32,36</t>
+          <t>22,9; 31,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 7,02</t>
+          <t>-2,93; 7,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 11,59</t>
+          <t>0,85; 11,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 28,41</t>
+          <t>-10,75; 29,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,92</t>
+          <t>-2,3; 4,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 13,38</t>
+          <t>6,3; 13,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 28,69</t>
+          <t>8,13; 28,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 17,54</t>
+          <t>-15,94; 18,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,74; 76,03</t>
+          <t>30,08; 75,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84,38; 144,42</t>
+          <t>85,56; 145,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 23,26</t>
+          <t>-7,9; 23,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 37,66</t>
+          <t>2,33; 36,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 87,64</t>
+          <t>-29,73; 91,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 14,9</t>
+          <t>-7,71; 15,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,55; 51,47</t>
+          <t>21,35; 48,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,38; 105,11</t>
+          <t>28,04; 105,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 0,44</t>
+          <t>-15,03; -0,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 9,28</t>
+          <t>-6,37; 9,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,17; 26,17</t>
+          <t>9,64; 25,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 2,98</t>
+          <t>-8,57; 2,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,0; 15,39</t>
+          <t>3,07; 14,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,22; 35,97</t>
+          <t>14,44; 34,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -0,11</t>
+          <t>-9,05; -0,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,44</t>
+          <t>0,84; 10,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,31; 30,59</t>
+          <t>15,34; 30,7</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 1,85</t>
+          <t>-45,83; -0,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 40,32</t>
+          <t>-19,84; 39,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31,4; 114,84</t>
+          <t>27,93; 104,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 11,73</t>
+          <t>-26,97; 10,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,54; 61,58</t>
+          <t>9,52; 56,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,86; 134,7</t>
+          <t>46,56; 129,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,5; -0,72</t>
+          <t>-28,8; -1,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,73; 41,07</t>
+          <t>2,63; 38,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48,11; 114,73</t>
+          <t>48,27; 112,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 16,09</t>
+          <t>-3,67; 16,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,5; 19,56</t>
+          <t>0,84; 18,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,27; 33,56</t>
+          <t>8,0; 33,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,96</t>
+          <t>2,07; 10,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,84; 23,13</t>
+          <t>13,86; 23,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,61; 36,38</t>
+          <t>27,33; 36,61</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,4</t>
+          <t>2,84; 10,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>13,66; 21,42</t>
+          <t>13,72; 22,02</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26,15; 34,83</t>
+          <t>25,98; 34,99</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 40,75</t>
+          <t>-7,87; 41,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,35; 49,38</t>
+          <t>2,11; 47,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18,15; 84,22</t>
+          <t>16,08; 82,46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,02; 45,6</t>
+          <t>7,29; 44,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>49,03; 97,2</t>
+          <t>48,99; 97,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>100,01; 155,78</t>
+          <t>97,43; 154,78</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,74; 38,2</t>
+          <t>9,27; 40,73</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>44,33; 79,91</t>
+          <t>43,9; 80,62</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>84,74; 128,91</t>
+          <t>84,07; 128,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,24</t>
+          <t>-2,98; 2,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,7</t>
+          <t>8,31; 13,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11,52; 28,38</t>
+          <t>11,56; 28,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,53</t>
+          <t>0,44; 5,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,71; 14,9</t>
+          <t>9,42; 14,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,01; 29,07</t>
+          <t>13,89; 29,04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,07</t>
+          <t>-0,47; 3,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,33</t>
+          <t>9,66; 13,29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>17,05; 28,07</t>
+          <t>16,67; 28,1</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 8,13</t>
+          <t>-9,56; 7,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>26,95; 48,35</t>
+          <t>26,92; 48,76</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38,95; 97,78</t>
+          <t>38,61; 97,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,42; 18,31</t>
+          <t>1,25; 17,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>30,03; 50,17</t>
+          <t>28,75; 48,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>44,01; 95,34</t>
+          <t>45,65; 94,28</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 10,45</t>
+          <t>-1,49; 10,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>30,44; 45,07</t>
+          <t>30,7; 44,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>54,93; 93,04</t>
+          <t>54,51; 93,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C01-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,77</t>
+          <t>31,07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,55</t>
+          <t>25,97</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28,57</t>
+          <t>28,93</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 7,15</t>
+          <t>-7,38; 6,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 22,18</t>
+          <t>7,19; 21,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,27; 38,11</t>
+          <t>24,55; 37,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 12,97</t>
+          <t>-3,7; 13,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 20,57</t>
+          <t>4,0; 20,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,1; 31,96</t>
+          <t>18,66; 33,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 7,15</t>
+          <t>-3,73; 7,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,91; 18,87</t>
+          <t>7,86; 18,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,43</t>
+          <t>24,4; 33,67</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 21,19</t>
+          <t>-18,66; 20,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,78; 67,63</t>
+          <t>17,86; 66,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,89; 115,82</t>
+          <t>58,96; 115,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 35,89</t>
+          <t>-7,56; 35,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 55,28</t>
+          <t>8,23; 55,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,8; 89,66</t>
+          <t>39,09; 94,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 19,89</t>
+          <t>-9,22; 20,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 53,01</t>
+          <t>18,64; 52,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,77; 94,43</t>
+          <t>57,93; 94,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34,82</t>
+          <t>34,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,86</t>
+          <t>30,49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>32,06</t>
+          <t>32,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 13,83</t>
+          <t>-1,98; 13,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 22,93</t>
+          <t>7,71; 23,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,84; 42,27</t>
+          <t>26,8; 41,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 15,8</t>
+          <t>0,05; 15,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 23,72</t>
+          <t>8,2; 24,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,92; 37,18</t>
+          <t>23,66; 38,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 11,79</t>
+          <t>1,02; 11,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 22,06</t>
+          <t>9,99; 21,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,18; 36,59</t>
+          <t>27,21; 37,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112,89%</t>
+          <t>111,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 51,33</t>
+          <t>-5,51; 48,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,21; 85,17</t>
+          <t>21,64; 88,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,86; 161,71</t>
+          <t>74,79; 153,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 45,97</t>
+          <t>-0,0; 45,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 71,55</t>
+          <t>19,1; 71,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,49; 113,95</t>
+          <t>55,52; 112,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 36,86</t>
+          <t>2,76; 37,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,07; 70,12</t>
+          <t>27,05; 68,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,31; 116,25</t>
+          <t>70,95; 118,53</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>28,4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,58</t>
+          <t>21,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,4</t>
+          <t>26,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 4,55</t>
+          <t>-6,71; 5,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 16,67</t>
+          <t>4,07; 17,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 31,51</t>
+          <t>21,5; 34,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 7,46</t>
+          <t>-12,56; 6,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 10,1</t>
+          <t>-12,89; 11,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 29,76</t>
+          <t>10,71; 31,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,29</t>
+          <t>-5,48; 3,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 13,75</t>
+          <t>2,03; 13,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 28,91</t>
+          <t>21,17; 32,02</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>104,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 19,09</t>
+          <t>-21,71; 22,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,56; 67,99</t>
+          <t>13,77; 77,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,29; 120,05</t>
+          <t>71,58; 146,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 24,96</t>
+          <t>-30,46; 25,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 35,95</t>
+          <t>-32,18; 39,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,19; 102,15</t>
+          <t>26,7; 111,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 15,68</t>
+          <t>-17,57; 15,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 50,65</t>
+          <t>6,55; 49,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 100,51</t>
+          <t>66,74; 123,63</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27,49</t>
+          <t>28,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,29</t>
+          <t>27,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21,79</t>
+          <t>27,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 4,01</t>
+          <t>-4,66; 3,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,05; 16,81</t>
+          <t>7,74; 16,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,9; 31,8</t>
+          <t>23,39; 32,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 7,27</t>
+          <t>-3,12; 7,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 11,18</t>
+          <t>0,75; 11,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 29,16</t>
+          <t>22,3; 31,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,14</t>
+          <t>-2,28; 4,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 13,05</t>
+          <t>6,01; 13,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,13; 28,65</t>
+          <t>24,15; 31,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113,23%</t>
+          <t>115,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 18,04</t>
+          <t>-17,84; 16,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,08; 75,48</t>
+          <t>28,17; 74,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,56; 145,69</t>
+          <t>85,98; 145,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 23,63</t>
+          <t>-8,34; 24,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 36,47</t>
+          <t>2,13; 38,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 91,55</t>
+          <t>60,96; 105,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 15,58</t>
+          <t>-7,65; 15,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,35; 48,94</t>
+          <t>20,22; 50,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28,04; 105,34</t>
+          <t>80,99; 119,97</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,13</t>
+          <t>15,67</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,99</t>
+          <t>21,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21,29</t>
+          <t>19,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,03; -0,42</t>
+          <t>-15,1; -0,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 9,34</t>
+          <t>-5,78; 9,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,64; 25,41</t>
+          <t>8,27; 22,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 2,8</t>
+          <t>-8,46; 2,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,07; 14,81</t>
+          <t>2,01; 14,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,44; 34,17</t>
+          <t>15,76; 26,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,29</t>
+          <t>-9,07; 0,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 10,23</t>
+          <t>1,24; 10,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,34; 30,7</t>
+          <t>14,31; 23,38</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,83; -0,63</t>
+          <t>-45,4; -1,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 39,59</t>
+          <t>-17,88; 40,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27,93; 104,84</t>
+          <t>26,22; 94,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 10,93</t>
+          <t>-25,89; 11,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,52; 56,95</t>
+          <t>5,28; 57,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,56; 129,29</t>
+          <t>47,24; 106,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,8; -1,12</t>
+          <t>-29,6; 0,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,63; 38,58</t>
+          <t>3,32; 40,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48,27; 112,68</t>
+          <t>43,88; 90,19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21,13</t>
+          <t>20,8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,12</t>
+          <t>32,24</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30,55</t>
+          <t>30,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 16,03</t>
+          <t>-3,46; 14,27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,84; 18,73</t>
+          <t>1,61; 19,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,0; 33,47</t>
+          <t>8,57; 32,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,68</t>
+          <t>2,25; 10,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,86; 23,26</t>
+          <t>13,62; 22,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,33; 36,61</t>
+          <t>28,02; 36,98</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,84; 10,81</t>
+          <t>2,81; 10,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>13,72; 22,02</t>
+          <t>14,02; 22,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25,98; 34,99</t>
+          <t>26,0; 34,61</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>125,28%</t>
+          <t>125,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>104,89%</t>
+          <t>104,36%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 41,32</t>
+          <t>-6,4; 36,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2,11; 47,9</t>
+          <t>2,81; 48,51</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16,08; 82,46</t>
+          <t>18,63; 81,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,29; 44,77</t>
+          <t>8,68; 44,49</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>48,99; 97,71</t>
+          <t>48,75; 96,52</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97,43; 154,78</t>
+          <t>99,74; 157,9</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,27; 40,73</t>
+          <t>9,09; 38,87</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>43,9; 80,62</t>
+          <t>45,48; 81,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>84,07; 128,68</t>
+          <t>83,78; 128,27</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23,33</t>
+          <t>27,03</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,38</t>
+          <t>27,81</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23,85</t>
+          <t>27,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,16</t>
+          <t>-3,24; 2,12</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8,31; 13,77</t>
+          <t>8,04; 13,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11,56; 28,45</t>
+          <t>24,25; 29,88</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,44</t>
+          <t>0,5; 5,36</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,42; 14,78</t>
+          <t>9,69; 14,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,89; 29,04</t>
+          <t>25,54; 30,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,09</t>
+          <t>-0,41; 3,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9,66; 13,29</t>
+          <t>9,84; 13,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16,67; 28,1</t>
+          <t>25,52; 29,11</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 7,54</t>
+          <t>-10,19; 7,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>26,92; 48,76</t>
+          <t>25,89; 47,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38,61; 97,51</t>
+          <t>77,28; 105,27</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,25; 17,89</t>
+          <t>1,54; 17,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>28,75; 48,98</t>
+          <t>29,65; 49,11</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,65; 94,28</t>
+          <t>77,78; 100,48</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 10,42</t>
+          <t>-1,3; 10,8</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>30,7; 44,89</t>
+          <t>31,06; 45,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>54,51; 93,3</t>
+          <t>80,45; 98,57</t>
         </is>
       </c>
     </row>
